--- a/result/train_info_resnet18_part_detrend_plr_stft_bin_win_anova.xlsx
+++ b/result/train_info_resnet18_part_detrend_plr_stft_bin_win_anova.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>train_loss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>test_loss</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
@@ -480,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5328270369617581</v>
+        <v>0.524739408763167</v>
       </c>
       <c r="C2" t="n">
         <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3415056770369851</v>
+        <v>0.4650489123615287</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8472686733556298</v>
+        <v>0.7987736900780379</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8563829787234043</v>
+        <v>0.9334406870638755</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8354336545589326</v>
+        <v>0.6445515196441809</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8457786116322702</v>
+        <v>0.7625520719140539</v>
       </c>
       <c r="I2" t="n">
-        <v>53.6830050945282</v>
+        <v>44.39424443244934</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2683847092955552</v>
+        <v>0.2775756530352989</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009997532801828658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1492160477802246</v>
+        <v>0.1984046785348266</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9409141583054627</v>
+        <v>0.9234485321441843</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9280898876404494</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9136397331356561</v>
+        <v>0.9184581171237954</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9394054878048781</v>
+        <v>0.9232488822652757</v>
       </c>
       <c r="I3" t="n">
-        <v>54.85818719863892</v>
+        <v>44.2118124961853</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1528682869154667</v>
+        <v>0.153171990703332</v>
       </c>
       <c r="C4" t="n">
         <v>0.0009990133642141358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1063444487993005</v>
+        <v>0.1180122263974802</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9606094388703085</v>
+        <v>0.9524340393905611</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9863067292644757</v>
+        <v>0.980330448465775</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9343958487768718</v>
+        <v>0.9236471460340994</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9596497906357061</v>
+        <v>0.9511450381679389</v>
       </c>
       <c r="I4" t="n">
-        <v>56.00569176673889</v>
+        <v>44.48024916648865</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0887698820635765</v>
+        <v>0.1018504653912021</v>
       </c>
       <c r="C5" t="n">
         <v>0.00099778098230154</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06951732399526256</v>
+        <v>0.07461876998973746</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9747305834262356</v>
+        <v>0.9730583426235601</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9627890173410405</v>
+        <v>0.9560557341907824</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9877687175685693</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9751189169410904</v>
+        <v>0.9736219756230672</v>
       </c>
       <c r="I5" t="n">
-        <v>56.90768098831177</v>
+        <v>40.33899188041687</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.06188697368287126</v>
+        <v>0.06217309035015546</v>
       </c>
       <c r="C6" t="n">
         <v>0.000996057350657239</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08618121644063197</v>
+        <v>0.0444561597786447</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9689706428836864</v>
+        <v>0.9856930509104422</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9540724793684966</v>
+        <v>0.978808914870296</v>
       </c>
       <c r="G6" t="n">
-        <v>0.985544848035582</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9695533272561532</v>
+        <v>0.9858325666973321</v>
       </c>
       <c r="I6" t="n">
-        <v>57.40319013595581</v>
+        <v>42.79225969314575</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.04662494663263112</v>
+        <v>0.05004579449341637</v>
       </c>
       <c r="C7" t="n">
         <v>0.0009938441702975688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06622715647843495</v>
+        <v>0.1087473751474227</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9760312151616499</v>
+        <v>0.9641397250092902</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9713761467889909</v>
+        <v>0.9439914923785891</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9810971089696071</v>
+        <v>0.9870274277242401</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9762124285450857</v>
+        <v>0.9650298967204204</v>
       </c>
       <c r="I7" t="n">
-        <v>58.43775939941406</v>
+        <v>43.89254784584045</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +642,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0357913983255202</v>
+        <v>0.03922272888288133</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009911436253643444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04260931550418357</v>
+        <v>0.04436772524588604</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9843924191750278</v>
+        <v>0.9845782237086584</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9833579881656804</v>
+        <v>0.9876911600149199</v>
       </c>
       <c r="G8" t="n">
-        <v>0.985544848035582</v>
+        <v>0.9814677538917717</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9844502036282858</v>
+        <v>0.9845696226064324</v>
       </c>
       <c r="I8" t="n">
-        <v>58.51920962333679</v>
+        <v>44.21856832504272</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +671,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03449391631155159</v>
+        <v>0.03768136957800863</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009879583809693736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03318717342042971</v>
+        <v>0.04249738557498417</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9890375325157934</v>
+        <v>0.9843924191750278</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9921671018276762</v>
+        <v>0.9840740740740741</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9859154929577465</v>
+        <v>0.9848035581912528</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9890314184792712</v>
+        <v>0.9844386809929604</v>
       </c>
       <c r="I9" t="n">
-        <v>58.50636100769043</v>
+        <v>41.27992939949036</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +700,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.03449263003381729</v>
+        <v>0.03305803251916849</v>
       </c>
       <c r="C10" t="n">
         <v>0.0009842915805643154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02884734714126143</v>
+        <v>0.03248899225345344</v>
       </c>
       <c r="E10" t="n">
-        <v>0.989223337049424</v>
+        <v>0.9895949461166852</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.994016454749439</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9851742031134173</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9893107261334316</v>
+        <v>0.9895755770662695</v>
       </c>
       <c r="I10" t="n">
-        <v>59.04395484924316</v>
+        <v>40.60504555702209</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +729,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02659860845035892</v>
+        <v>0.02505516631460495</v>
       </c>
       <c r="C11" t="n">
         <v>0.0009801468428384714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03022224500898641</v>
+        <v>0.0223898700819545</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9888517279821628</v>
+        <v>0.992196209587514</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9936377245508982</v>
+        <v>0.9940476190476191</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9840622683469237</v>
+        <v>0.9903632320237212</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9888268156424581</v>
+        <v>0.9922020051986632</v>
       </c>
       <c r="I11" t="n">
-        <v>59.27356624603271</v>
+        <v>43.16038537025452</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +758,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0219760712485127</v>
+        <v>0.02587959137393188</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009755282581475767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03726889320770444</v>
+        <v>0.04342751099801927</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9869936826458565</v>
+        <v>0.9866220735785953</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9792122538293216</v>
+        <v>0.9910246821241586</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9822090437361009</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9871323529411765</v>
+        <v>0.9865971705137752</v>
       </c>
       <c r="I12" t="n">
-        <v>58.29129028320312</v>
+        <v>42.98764181137085</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +787,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0165860910028925</v>
+        <v>0.02556217641421647</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009704403844771127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02454564735813813</v>
+        <v>0.02429880575413303</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9918246005202527</v>
+        <v>0.9916387959866221</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9893067846607669</v>
+        <v>0.9893028402803393</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9918669131238448</v>
+        <v>0.9916805324459235</v>
       </c>
       <c r="I13" t="n">
-        <v>57.98350548744202</v>
+        <v>41.17072868347168</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +816,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02139019526318311</v>
+        <v>0.01790631728752428</v>
       </c>
       <c r="C14" t="n">
         <v>0.0009648882429441257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02632074375132639</v>
+        <v>0.01784757470060071</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9899665551839465</v>
+        <v>0.9933110367892977</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9966190833959429</v>
+        <v>0.9966417910447761</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9833209785025945</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9899253731343284</v>
+        <v>0.9933060617329862</v>
       </c>
       <c r="I14" t="n">
-        <v>57.78253960609436</v>
+        <v>41.97758197784424</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +845,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01736366844987595</v>
+        <v>0.01590828064773628</v>
       </c>
       <c r="C15" t="n">
         <v>0.0009588773128419905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0395503788445966</v>
+        <v>0.04059426895323479</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9842066146413972</v>
+        <v>0.9866220735785953</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9858683525474154</v>
+        <v>0.977802037845706</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9825796886582654</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9842212734360497</v>
+        <v>0.9867792875504958</v>
       </c>
       <c r="I15" t="n">
-        <v>57.55726456642151</v>
+        <v>45.79209566116333</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +874,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01286738619204864</v>
+        <v>0.01768679552054267</v>
       </c>
       <c r="C16" t="n">
         <v>0.0009524135262330098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.04613945625860436</v>
+        <v>0.02543005946928569</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9855072463768116</v>
+        <v>0.9918246005202527</v>
       </c>
       <c r="F16" t="n">
-        <v>0.984109386548411</v>
+        <v>0.9911176905995559</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9870274277242401</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9855662472242783</v>
+        <v>0.9918518518518519</v>
       </c>
       <c r="I16" t="n">
-        <v>57.47425770759583</v>
+        <v>45.04291296005249</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +903,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01926548573544973</v>
+        <v>0.01587984736044373</v>
       </c>
       <c r="C17" t="n">
         <v>0.0009455032620941839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01266302029363522</v>
+        <v>0.03170255820557769</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9890375325157934</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9955555555555555</v>
+        <v>0.992534527808884</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.985544848035582</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9959244164505372</v>
+        <v>0.989027338664683</v>
       </c>
       <c r="I17" t="n">
-        <v>58.2429678440094</v>
+        <v>45.44410443305969</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +932,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01370302495987261</v>
+        <v>0.01618965167568687</v>
       </c>
       <c r="C18" t="n">
         <v>0.0009381533400219318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05178727182197077</v>
+        <v>0.02234856374352118</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9838350055741361</v>
+        <v>0.9938684503901896</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9946949602122016</v>
+        <v>0.9904306220095693</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9729429206819866</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H18" t="n">
-        <v>0.983698707138842</v>
+        <v>0.9939058171745152</v>
       </c>
       <c r="I18" t="n">
-        <v>58.57079601287842</v>
+        <v>45.08598256111145</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +961,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01934367098036234</v>
+        <v>0.01107565598663294</v>
       </c>
       <c r="C19" t="n">
         <v>0.0009303710135019719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03761444507073017</v>
+        <v>0.01228260382195864</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9881085098476403</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9988636363636364</v>
+        <v>0.9966617210682492</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9773906597479615</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9880104908205321</v>
+        <v>0.996292176492399</v>
       </c>
       <c r="I19" t="n">
-        <v>58.63484883308411</v>
+        <v>45.13814115524292</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +990,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01116752405175652</v>
+        <v>0.01341382873659281</v>
       </c>
       <c r="C20" t="n">
         <v>0.0009221639627510076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01375725698244154</v>
+        <v>0.02384415220041462</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9927536231884058</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9948128936643201</v>
+        <v>0.9966380276428838</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9888806523350631</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9949972206781545</v>
+        <v>0.9927441860465116</v>
       </c>
       <c r="I20" t="n">
-        <v>59.10340189933777</v>
+        <v>44.72258758544922</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1019,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.006379196804329511</v>
+        <v>0.0123852798369815</v>
       </c>
       <c r="C21" t="n">
         <v>0.000913540287137281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03482832519856582</v>
+        <v>0.0249679689264807</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9897807506503159</v>
+        <v>0.9914529914529915</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9878183831672204</v>
+        <v>0.9973743435858965</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9918458117123795</v>
+        <v>0.985544848035582</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9898280007397817</v>
+        <v>0.9914243102162565</v>
       </c>
       <c r="I21" t="n">
-        <v>59.65641975402832</v>
+        <v>45.17146277427673</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1048,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01112219794055938</v>
+        <v>0.01165579081918993</v>
       </c>
       <c r="C22" t="n">
         <v>0.0009045084971874739</v>
       </c>
       <c r="D22" t="n">
-        <v>0.03273129285838952</v>
+        <v>0.01870819448472583</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9886659234485321</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9936353425683264</v>
+        <v>0.9977595220313666</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9836916234247591</v>
+        <v>0.9903632320237212</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9886384801639039</v>
+        <v>0.9940476190476191</v>
       </c>
       <c r="I22" t="n">
-        <v>58.9408061504364</v>
+        <v>44.72477674484253</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1077,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01404757894955194</v>
+        <v>0.01053242664975822</v>
       </c>
       <c r="C23" t="n">
         <v>0.0008950775061878453</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02027955518489503</v>
+        <v>0.03172772558165361</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9944258639910813</v>
+        <v>0.990709773318469</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9915254237288136</v>
+        <v>0.9955089820359282</v>
       </c>
       <c r="G23" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9859154929577465</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9944567627494457</v>
+        <v>0.9906890130353817</v>
       </c>
       <c r="I23" t="n">
-        <v>58.49047780036926</v>
+        <v>45.02640247344971</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1106,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.005732362842469299</v>
+        <v>0.01067967175342676</v>
       </c>
       <c r="C24" t="n">
         <v>0.0008852566213878948</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01592382671951674</v>
+        <v>0.02610094084976755</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9951690821256038</v>
+        <v>0.9912671869193609</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9915378955114055</v>
+        <v>0.9867792875504958</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9988880652335063</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9951994091580503</v>
+        <v>0.9913300129127467</v>
       </c>
       <c r="I24" t="n">
-        <v>58.08997368812561</v>
+        <v>44.95080590248108</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01242097476667678</v>
+        <v>0.009630387134549884</v>
       </c>
       <c r="C25" t="n">
         <v>0.0008750555348152299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01921617744079606</v>
+        <v>0.01069015853142537</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9918759231905465</v>
+        <v>0.9959259259259259</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9937106918238994</v>
+        <v>0.9962949240459429</v>
       </c>
       <c r="I25" t="n">
-        <v>57.43764162063599</v>
+        <v>43.48690748214722</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1164,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.006324016079936195</v>
+        <v>0.009598908173117192</v>
       </c>
       <c r="C26" t="n">
         <v>0.0008644843137107058</v>
       </c>
       <c r="D26" t="n">
-        <v>0.008818744292102835</v>
+        <v>0.02818561605495206</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9966555183946488</v>
+        <v>0.9879227053140096</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9985119047619048</v>
+        <v>0.996605054696341</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9792438843587843</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9966580022279985</v>
+        <v>0.9878481959244718</v>
       </c>
       <c r="I26" t="n">
-        <v>57.18555617332458</v>
+        <v>42.6219310760498</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1193,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.009097702344548387</v>
+        <v>0.007477102600766231</v>
       </c>
       <c r="C27" t="n">
         <v>0.0008535533905932738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00958124877388669</v>
+        <v>0.007806292659686668</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9964697138610182</v>
+        <v>0.9975845410628019</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9959274342835986</v>
+        <v>0.9974064468321601</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9964808297832932</v>
+        <v>0.9975912544005929</v>
       </c>
       <c r="I27" t="n">
-        <v>57.66213631629944</v>
+        <v>43.04714632034302</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1222,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.007535185331090073</v>
+        <v>0.006567475231169405</v>
       </c>
       <c r="C28" t="n">
         <v>0.0008422735529643445</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01618995387799426</v>
+        <v>0.01615746553844587</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9962839093273876</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9948263118994827</v>
+        <v>0.9973929236499068</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H28" t="n">
-        <v>0.996299037749815</v>
+        <v>0.9949842095485789</v>
       </c>
       <c r="I28" t="n">
-        <v>57.80321669578552</v>
+        <v>44.60321569442749</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1251,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.006852556027156174</v>
+        <v>0.009969847672858665</v>
       </c>
       <c r="C29" t="n">
         <v>0.000830655932661826</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0135449380041689</v>
+        <v>0.01769663637487449</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9946116685247121</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9959213941416388</v>
+        <v>0.9926172019195275</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9957367933271548</v>
+        <v>0.9946365822082486</v>
       </c>
       <c r="I29" t="n">
-        <v>58.03645968437195</v>
+        <v>44.75879883766174</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1280,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.007947284293755597</v>
+        <v>0.005971214049256855</v>
       </c>
       <c r="C30" t="n">
         <v>0.000818711994874345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01678796281616216</v>
+        <v>0.01009257067945602</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9972129319955407</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9977636973537085</v>
+        <v>0.9963004069552349</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9922164566345441</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9949823452889798</v>
+        <v>0.9972227365302722</v>
       </c>
       <c r="I30" t="n">
-        <v>58.54056739807129</v>
+        <v>44.51578497886658</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1309,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.007084619809245346</v>
+        <v>0.004027521980718554</v>
       </c>
       <c r="C31" t="n">
         <v>0.0008064535268264884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01426904539550496</v>
+        <v>0.01777692408803666</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9981378026070763</v>
+        <v>0.9959138187221397</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9957272896154561</v>
+        <v>0.9948051948051948</v>
       </c>
       <c r="I31" t="n">
-        <v>58.69823265075684</v>
+        <v>41.25569891929626</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1338,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.005285306490737372</v>
+        <v>0.009097111841830652</v>
       </c>
       <c r="C32" t="n">
         <v>0.0007938926261462368</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01407853392946993</v>
+        <v>0.006705914592703535</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9977703455964325</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9918968692449356</v>
+        <v>0.9985152190051967</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9950120081285794</v>
+        <v>0.9977744807121661</v>
       </c>
       <c r="I32" t="n">
-        <v>59.01570415496826</v>
+        <v>40.55767798423767</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1367,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.006992078612116722</v>
+        <v>0.00640213573700293</v>
       </c>
       <c r="C33" t="n">
         <v>0.0007810416889260655</v>
       </c>
       <c r="D33" t="n">
-        <v>0.02535481973023362</v>
+        <v>0.01039513494494912</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9918246005202527</v>
+        <v>0.9964697138610182</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9966317365269461</v>
+        <v>0.9970315398886828</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9870274277242401</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9918063314711359</v>
+        <v>0.9964769145188207</v>
       </c>
       <c r="I33" t="n">
-        <v>58.98621225357056</v>
+        <v>40.82619833946228</v>
       </c>
     </row>
     <row r="34">
@@ -1408,13 +1396,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.003937185111726109</v>
+        <v>0.004317618274123451</v>
       </c>
       <c r="C34" t="n">
         <v>0.0007679133974894984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01249274988449489</v>
+        <v>0.01382724810862772</v>
       </c>
       <c r="E34" t="n">
         <v>0.9957264957264957</v>
@@ -1429,7 +1417,7 @@
         <v>0.9957525392428439</v>
       </c>
       <c r="I34" t="n">
-        <v>58.91553807258606</v>
+        <v>41.10526394844055</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1425,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.005233826345582278</v>
+        <v>0.007787215628863012</v>
       </c>
       <c r="C35" t="n">
         <v>0.0007545207078751858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0314149817381373</v>
+        <v>0.01265228027015041</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9908955778520996</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9835706462212487</v>
+        <v>0.9973968017850502</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9909876770277727</v>
+        <v>0.9957304622238723</v>
       </c>
       <c r="I35" t="n">
-        <v>58.48190951347351</v>
+        <v>40.99690985679626</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1454,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.005661592918617732</v>
+        <v>0.001444580136442569</v>
       </c>
       <c r="C36" t="n">
         <v>0.0007408768370508578</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01214478481589253</v>
+        <v>0.009280405915252936</v>
       </c>
       <c r="E36" t="n">
         <v>0.9977703455964325</v>
       </c>
       <c r="F36" t="n">
-        <v>0.997039230199852</v>
+        <v>0.9985152190051967</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9977777777777778</v>
+        <v>0.9977744807121661</v>
       </c>
       <c r="I36" t="n">
-        <v>57.73241972923279</v>
+        <v>43.90452218055725</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1483,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.001675952632109041</v>
+        <v>0.005741531784862408</v>
       </c>
       <c r="C37" t="n">
         <v>0.0007269952498697736</v>
       </c>
       <c r="D37" t="n">
-        <v>0.009352710840067217</v>
+        <v>0.01171838023433796</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9977703455964325</v>
+        <v>0.99702712746191</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9988855869242199</v>
+        <v>0.9992553983618764</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H37" t="n">
-        <v>0.997773654916512</v>
+        <v>0.9970282317979198</v>
       </c>
       <c r="I37" t="n">
-        <v>57.6069598197937</v>
+        <v>45.85230565071106</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1512,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.002157171833318817</v>
+        <v>0.00359280371537148</v>
       </c>
       <c r="C38" t="n">
         <v>0.0007128896457825365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.003131871066131502</v>
+        <v>0.009575328286044266</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9988851727982163</v>
+        <v>0.99702712746191</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9985185185185185</v>
+        <v>0.9981426448736999</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9992587101556709</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9988884772137829</v>
+        <v>0.9970315398886828</v>
       </c>
       <c r="I38" t="n">
-        <v>57.01882433891296</v>
+        <v>41.41800093650818</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1541,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0110255963039275</v>
+        <v>0.003174097437498349</v>
       </c>
       <c r="C39" t="n">
         <v>0.0006985739453173904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01195443788863744</v>
+        <v>0.00854820334772952</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9977703455964325</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9933628318584071</v>
+        <v>0.9974074074074074</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9959334565619223</v>
+        <v>0.9977769544275658</v>
       </c>
       <c r="I39" t="n">
-        <v>56.99908518791199</v>
+        <v>45.25328207015991</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1570,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.004200987396812804</v>
+        <v>0.001115728554153492</v>
       </c>
       <c r="C40" t="n">
         <v>0.0006840622763423392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.04265904193565393</v>
+        <v>0.007709483387158981</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9890375325157934</v>
+        <v>0.9981419546636938</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9896103896103896</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9885100074128984</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H40" t="n">
-        <v>0.98905989245318</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="I40" t="n">
-        <v>57.01137399673462</v>
+        <v>40.75353765487671</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1599,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.004186356626265333</v>
+        <v>0.004119960812785118</v>
       </c>
       <c r="C41" t="n">
         <v>0.0006693689601226459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.01850414023355634</v>
+        <v>0.02123505352378393</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9927536231884058</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9962700484893696</v>
+        <v>0.9996242014280345</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9899925871015567</v>
+        <v>0.9859154929577465</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9931213980293735</v>
+        <v>0.9927225228587423</v>
       </c>
       <c r="I41" t="n">
-        <v>57.8453197479248</v>
+        <v>41.22620368003845</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.0006158335119565158</v>
+        <v>0.004382269616732046</v>
       </c>
       <c r="C42" t="n">
         <v>0.0006545084971874739</v>
       </c>
       <c r="D42" t="n">
-        <v>0.005024505577910009</v>
+        <v>0.01110177041280693</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9988851727982163</v>
+        <v>0.9964697138610182</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9988880652335063</v>
+        <v>0.993006993006993</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9988880652335063</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9988880652335063</v>
+        <v>0.9964912280701754</v>
       </c>
       <c r="I42" t="n">
-        <v>58.60698390007019</v>
+        <v>41.32605338096619</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1657,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>3.39568266326075e-05</v>
+        <v>0.0003292776081162124</v>
       </c>
       <c r="C43" t="n">
         <v>0.0006394955530196148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.003715567447355267</v>
+        <v>0.004391039372552389</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9986993682645856</v>
+        <v>0.9981419546636938</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9981488337652721</v>
+        <v>0.9970414201183432</v>
       </c>
       <c r="G43" t="n">
         <v>0.9992587101556709</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9987034636043712</v>
+        <v>0.9981488337652721</v>
       </c>
       <c r="I43" t="n">
-        <v>58.34049129486084</v>
+        <v>41.35185289382935</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1686,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>8.239114684864407e-06</v>
+        <v>5.893499121597186e-05</v>
       </c>
       <c r="C44" t="n">
         <v>0.0006243449435824275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.003071658960788699</v>
+        <v>0.006068735716417618</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9988851727982163</v>
+        <v>0.9979561501300632</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9985185185185185</v>
+        <v>0.9977769544275658</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9992587101556709</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9988884772137829</v>
+        <v>0.9979618306466556</v>
       </c>
       <c r="I44" t="n">
-        <v>58.80358242988586</v>
+        <v>47.70871424674988</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1715,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.008564016310668868</v>
+        <v>0.007474657056338498</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006090716206982715</v>
       </c>
       <c r="D45" t="n">
-        <v>0.02178733956348427</v>
+        <v>0.03732665199541883</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9953548866592344</v>
+        <v>0.987736900780379</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9973948641607741</v>
+        <v>0.9816983894582724</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9953574744661096</v>
+        <v>0.9878453038674033</v>
       </c>
       <c r="I45" t="n">
-        <v>58.82355546951294</v>
+        <v>47.76113986968994</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1744,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.00464712491566861</v>
+        <v>0.004187617448521692</v>
       </c>
       <c r="C46" t="n">
         <v>0.0005936906572928626</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01014106153858724</v>
+        <v>0.009644188434690773</v>
       </c>
       <c r="E46" t="n">
-        <v>0.99702712746191</v>
+        <v>0.9975845410628019</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9959319526627219</v>
+        <v>0.9963031423290203</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9988880652335063</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9970381340244354</v>
+        <v>0.9975939292985379</v>
       </c>
       <c r="I46" t="n">
-        <v>59.31805205345154</v>
+        <v>58.36152648925781</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1773,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.001379161709070255</v>
+        <v>0.0001897516506071609</v>
       </c>
       <c r="C47" t="n">
         <v>0.0005782172325201157</v>
       </c>
       <c r="D47" t="n">
-        <v>0.004323807193218837</v>
+        <v>0.009061233302755283</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9983277591973244</v>
+        <v>0.9975845410628019</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9981474620229714</v>
+        <v>0.9955703211517165</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9996293550778355</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9983324068927182</v>
+        <v>0.9975957092657666</v>
       </c>
       <c r="I47" t="n">
-        <v>59.13160228729248</v>
+        <v>54.14999628067017</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1802,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>9.810993332822049e-05</v>
+        <v>4.271646347697012e-05</v>
       </c>
       <c r="C48" t="n">
         <v>0.0005626666167821524</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0115778783037981</v>
+        <v>0.008104571052213476</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9973987365291713</v>
+        <v>0.9981419546636938</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9992559523809523</v>
+        <v>0.9966740576496674</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9996293550778355</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9974006683995544</v>
+        <v>0.9981495188749074</v>
       </c>
       <c r="I48" t="n">
-        <v>58.41173887252808</v>
+        <v>54.50462579727173</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1831,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.006609589980191321</v>
+        <v>4.615149913357909e-05</v>
       </c>
       <c r="C49" t="n">
         <v>0.0005470541566592573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.005787745217432164</v>
+        <v>0.008821408020504415</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9983277591973244</v>
+        <v>0.998513563730955</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9992573338284441</v>
+        <v>0.9974112426035503</v>
       </c>
       <c r="G49" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9996293550778355</v>
       </c>
       <c r="H49" t="n">
-        <v>0.998330550918197</v>
+        <v>0.9985190670122177</v>
       </c>
       <c r="I49" t="n">
-        <v>57.8740975856781</v>
+        <v>52.2706778049469</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1860,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0009142258570410616</v>
+        <v>1.666455823945769e-05</v>
       </c>
       <c r="C50" t="n">
         <v>0.000531395259764657</v>
       </c>
       <c r="D50" t="n">
-        <v>0.005642426197148231</v>
+        <v>0.006720838599114929</v>
       </c>
       <c r="E50" t="n">
         <v>0.9981419546636938</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9985163204747775</v>
+        <v>0.9970414201183432</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9992587101556709</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9981460882461994</v>
+        <v>0.9981488337652721</v>
       </c>
       <c r="I50" t="n">
-        <v>57.32750821113586</v>
+        <v>52.37026262283325</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1889,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.001699545840531746</v>
+        <v>3.826526971927862e-06</v>
       </c>
       <c r="C51" t="n">
         <v>0.0005157053795390644</v>
       </c>
       <c r="D51" t="n">
-        <v>0.004993281136482717</v>
+        <v>0.006367904281076156</v>
       </c>
       <c r="E51" t="n">
-        <v>0.998513563730955</v>
+        <v>0.9983277591973244</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9988872403560831</v>
+        <v>0.9974102848686645</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9992587101556709</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9985168705969596</v>
+        <v>0.9983336419181633</v>
       </c>
       <c r="I51" t="n">
-        <v>57.36124157905579</v>
+        <v>52.71077704429626</v>
       </c>
     </row>
   </sheetData>
